--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130226257</v>
+        <v>130228510</v>
       </c>
       <c r="B2" t="n">
         <v>98833</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537794</v>
+        <v>537793</v>
       </c>
       <c r="R2" t="n">
-        <v>6467943</v>
+        <v>6467967</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130227792</v>
+        <v>130226257</v>
       </c>
       <c r="B3" t="n">
         <v>98833</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537821</v>
+        <v>537794</v>
       </c>
       <c r="R3" t="n">
-        <v>6467932</v>
+        <v>6467943</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130228510</v>
+        <v>130227792</v>
       </c>
       <c r="B4" t="n">
         <v>98833</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537793</v>
+        <v>537821</v>
       </c>
       <c r="R4" t="n">
-        <v>6467967</v>
+        <v>6467932</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130228510</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130226257</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130227792</v>
       </c>
       <c r="B4" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130226327</v>
+        <v>130226328</v>
       </c>
       <c r="B5" t="n">
-        <v>96322</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130226328</v>
+        <v>130226327</v>
       </c>
       <c r="B6" t="n">
-        <v>98833</v>
+        <v>96409</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
         <v>130226681</v>
       </c>
       <c r="B7" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>130227576</v>
       </c>
       <c r="B8" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>130228067</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>130226435</v>
       </c>
       <c r="B10" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>130226109</v>
       </c>
       <c r="B11" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>130228095</v>
       </c>
       <c r="B13" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>130226897</v>
       </c>
       <c r="B14" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>130226951</v>
       </c>
       <c r="B15" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>130226578</v>
       </c>
       <c r="B16" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130226328</v>
+        <v>130226327</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>96409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130226327</v>
+        <v>130226328</v>
       </c>
       <c r="B6" t="n">
-        <v>96409</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130226327</v>
+        <v>130226328</v>
       </c>
       <c r="B5" t="n">
-        <v>96409</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130226328</v>
+        <v>130226327</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>96409</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130227792</v>
+        <v>130228510</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537821</v>
+        <v>537793</v>
       </c>
       <c r="R2" t="n">
-        <v>6467932</v>
+        <v>6467967</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130228510</v>
+        <v>130226257</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537793</v>
+        <v>537794</v>
       </c>
       <c r="R3" t="n">
-        <v>6467967</v>
+        <v>6467943</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130226257</v>
+        <v>130227792</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537794</v>
+        <v>537821</v>
       </c>
       <c r="R4" t="n">
-        <v>6467943</v>
+        <v>6467932</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130226327</v>
+        <v>130226328</v>
       </c>
       <c r="B5" t="n">
-        <v>96409</v>
+        <v>98923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130226328</v>
+        <v>130226327</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>96412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
         <v>130226681</v>
       </c>
       <c r="B7" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>130226435</v>
       </c>
       <c r="B10" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>130226109</v>
       </c>
       <c r="B11" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>130228095</v>
       </c>
       <c r="B13" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>130226897</v>
       </c>
       <c r="B14" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>130226578</v>
       </c>
       <c r="B16" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130228510</v>
       </c>
       <c r="B2" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130226257</v>
       </c>
       <c r="B3" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130227792</v>
       </c>
       <c r="B4" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>130226328</v>
       </c>
       <c r="B5" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130226327</v>
       </c>
       <c r="B6" t="n">
-        <v>96412</v>
+        <v>96438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130226681</v>
       </c>
       <c r="B7" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>130227576</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>130228067</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>130226435</v>
       </c>
       <c r="B10" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>130226109</v>
       </c>
       <c r="B11" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>130228095</v>
       </c>
       <c r="B13" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>130226897</v>
       </c>
       <c r="B14" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>130226951</v>
       </c>
       <c r="B15" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>130226578</v>
       </c>
       <c r="B16" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130228510</v>
+        <v>130227792</v>
       </c>
       <c r="B2" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537793</v>
+        <v>537821</v>
       </c>
       <c r="R2" t="n">
-        <v>6467967</v>
+        <v>6467932</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130226257</v>
+        <v>130228510</v>
       </c>
       <c r="B3" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537794</v>
+        <v>537793</v>
       </c>
       <c r="R3" t="n">
-        <v>6467943</v>
+        <v>6467967</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130227792</v>
+        <v>130226257</v>
       </c>
       <c r="B4" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537821</v>
+        <v>537794</v>
       </c>
       <c r="R4" t="n">
-        <v>6467932</v>
+        <v>6467943</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130226328</v>
+        <v>130226327</v>
       </c>
       <c r="B5" t="n">
-        <v>98949</v>
+        <v>96439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130226327</v>
+        <v>130226328</v>
       </c>
       <c r="B6" t="n">
-        <v>96438</v>
+        <v>98950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
         <v>130226681</v>
       </c>
       <c r="B7" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>130226435</v>
       </c>
       <c r="B10" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>130226109</v>
       </c>
       <c r="B11" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>130228095</v>
       </c>
       <c r="B13" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>130226897</v>
       </c>
       <c r="B14" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>130226578</v>
       </c>
       <c r="B16" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130227792</v>
+        <v>130228510</v>
       </c>
       <c r="B2" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537821</v>
+        <v>537793</v>
       </c>
       <c r="R2" t="n">
-        <v>6467932</v>
+        <v>6467967</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130228510</v>
+        <v>130226257</v>
       </c>
       <c r="B3" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537793</v>
+        <v>537794</v>
       </c>
       <c r="R3" t="n">
-        <v>6467967</v>
+        <v>6467943</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130226257</v>
+        <v>130227792</v>
       </c>
       <c r="B4" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537794</v>
+        <v>537821</v>
       </c>
       <c r="R4" t="n">
-        <v>6467943</v>
+        <v>6467932</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130226327</v>
+        <v>130226328</v>
       </c>
       <c r="B5" t="n">
-        <v>96439</v>
+        <v>98951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130226328</v>
+        <v>130226327</v>
       </c>
       <c r="B6" t="n">
-        <v>98950</v>
+        <v>96440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
         <v>130226681</v>
       </c>
       <c r="B7" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>130226435</v>
       </c>
       <c r="B10" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>130226109</v>
       </c>
       <c r="B11" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>130228095</v>
       </c>
       <c r="B13" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>130226897</v>
       </c>
       <c r="B14" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>130226578</v>
       </c>
       <c r="B16" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130228510</v>
+        <v>130227792</v>
       </c>
       <c r="B2" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537793</v>
+        <v>537821</v>
       </c>
       <c r="R2" t="n">
-        <v>6467967</v>
+        <v>6467932</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130226257</v>
+        <v>130228510</v>
       </c>
       <c r="B3" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537794</v>
+        <v>537793</v>
       </c>
       <c r="R3" t="n">
-        <v>6467943</v>
+        <v>6467967</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130227792</v>
+        <v>130226257</v>
       </c>
       <c r="B4" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537821</v>
+        <v>537794</v>
       </c>
       <c r="R4" t="n">
-        <v>6467932</v>
+        <v>6467943</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>130226328</v>
       </c>
       <c r="B5" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130226327</v>
       </c>
       <c r="B6" t="n">
-        <v>96440</v>
+        <v>96442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130226681</v>
       </c>
       <c r="B7" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>130227576</v>
       </c>
       <c r="B8" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hasse Andersson</t>
+          <t>Hasse Andersson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1374,7 +1374,7 @@
         <v>130228067</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>130226435</v>
       </c>
       <c r="B10" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>130226109</v>
       </c>
       <c r="B11" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>130228095</v>
       </c>
       <c r="B13" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>130226897</v>
       </c>
       <c r="B14" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>130226951</v>
       </c>
       <c r="B15" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>130226578</v>
       </c>
       <c r="B16" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130227792</v>
+        <v>130228510</v>
       </c>
       <c r="B2" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537821</v>
+        <v>537793</v>
       </c>
       <c r="R2" t="n">
-        <v>6467932</v>
+        <v>6467967</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130228510</v>
+        <v>130226257</v>
       </c>
       <c r="B3" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537793</v>
+        <v>537794</v>
       </c>
       <c r="R3" t="n">
-        <v>6467967</v>
+        <v>6467943</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130226257</v>
+        <v>130227792</v>
       </c>
       <c r="B4" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537794</v>
+        <v>537821</v>
       </c>
       <c r="R4" t="n">
-        <v>6467943</v>
+        <v>6467932</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>130226328</v>
       </c>
       <c r="B5" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>130226327</v>
       </c>
       <c r="B6" t="n">
-        <v>96442</v>
+        <v>96446</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>130226681</v>
       </c>
       <c r="B7" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hasse Andersson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Hasse Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1479,7 +1479,7 @@
         <v>130226435</v>
       </c>
       <c r="B10" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>130226109</v>
       </c>
       <c r="B11" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>130228095</v>
       </c>
       <c r="B13" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>130226897</v>
       </c>
       <c r="B14" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>130226578</v>
       </c>
       <c r="B16" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130226328</v>
+        <v>130226327</v>
       </c>
       <c r="B5" t="n">
-        <v>98957</v>
+        <v>96446</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130226327</v>
+        <v>130226328</v>
       </c>
       <c r="B6" t="n">
-        <v>96446</v>
+        <v>98957</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -2094,7 +2094,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130226578</v>
+        <v>130226603</v>
       </c>
       <c r="B16" t="n">
         <v>98957</v>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130226327</v>
+        <v>130226328</v>
       </c>
       <c r="B5" t="n">
-        <v>96446</v>
+        <v>98957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130226328</v>
+        <v>130226327</v>
       </c>
       <c r="B6" t="n">
-        <v>98957</v>
+        <v>96446</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -2094,7 +2094,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130226603</v>
+        <v>130226578</v>
       </c>
       <c r="B16" t="n">
         <v>98957</v>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2198,6 +2198,223 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131470166</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lilla Bråstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>537744</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6467923</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131469633</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91838</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lilla Bråstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>537717</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6467941</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -2203,7 +2203,7 @@
         <v>131470166</v>
       </c>
       <c r="B17" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>131469633</v>
       </c>
       <c r="B18" t="n">
-        <v>91838</v>
+        <v>91839</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2203,7 +2203,7 @@
         <v>131470166</v>
       </c>
       <c r="B17" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>131469633</v>
       </c>
       <c r="B18" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2414,6 +2414,103 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131553226</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58050</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lilla Bråstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>537789</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6467828</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -2203,7 +2203,7 @@
         <v>131470166</v>
       </c>
       <c r="B17" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>131469633</v>
       </c>
       <c r="B18" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>131553226</v>
       </c>
       <c r="B19" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -2203,7 +2203,7 @@
         <v>131470166</v>
       </c>
       <c r="B17" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>131469633</v>
       </c>
       <c r="B18" t="n">
-        <v>91843</v>
+        <v>91849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>131553226</v>
       </c>
       <c r="B19" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -2203,7 +2203,7 @@
         <v>131470166</v>
       </c>
       <c r="B17" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -2203,7 +2203,7 @@
         <v>131470166</v>
       </c>
       <c r="B17" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>131469633</v>
       </c>
       <c r="B18" t="n">
-        <v>91849</v>
+        <v>91850</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>131553226</v>
       </c>
       <c r="B19" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -2203,7 +2203,7 @@
         <v>131470166</v>
       </c>
       <c r="B17" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>131469633</v>
       </c>
       <c r="B18" t="n">
-        <v>91850</v>
+        <v>91853</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>131553226</v>
       </c>
       <c r="B19" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -2203,7 +2203,7 @@
         <v>131470166</v>
       </c>
       <c r="B17" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>131469633</v>
       </c>
       <c r="B18" t="n">
-        <v>91853</v>
+        <v>91859</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>131553226</v>
       </c>
       <c r="B19" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -2203,7 +2203,7 @@
         <v>131470166</v>
       </c>
       <c r="B17" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>131469633</v>
       </c>
       <c r="B18" t="n">
-        <v>91859</v>
+        <v>91862</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>131553226</v>
       </c>
       <c r="B19" t="n">
-        <v>58063</v>
+        <v>58066</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -2203,7 +2203,7 @@
         <v>131470166</v>
       </c>
       <c r="B17" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>131469633</v>
       </c>
       <c r="B18" t="n">
-        <v>91862</v>
+        <v>91867</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>131553226</v>
       </c>
       <c r="B19" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -2203,7 +2203,7 @@
         <v>131470166</v>
       </c>
       <c r="B17" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>131469633</v>
       </c>
       <c r="B18" t="n">
-        <v>91867</v>
+        <v>91869</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>131553226</v>
       </c>
       <c r="B19" t="n">
-        <v>58071</v>
+        <v>58073</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130228510</v>
+        <v>130226327</v>
       </c>
       <c r="B2" t="n">
-        <v>98957</v>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537793</v>
+        <v>537772</v>
       </c>
       <c r="R2" t="n">
-        <v>6467967</v>
+        <v>6467983</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,45 +772,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130226257</v>
+        <v>131469633</v>
       </c>
       <c r="B3" t="n">
-        <v>98957</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lilla Bråstorp, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537794</v>
+        <v>537717</v>
       </c>
       <c r="R3" t="n">
-        <v>6467943</v>
+        <v>6467941</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -862,52 +876,60 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hasse Andersson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130227792</v>
+        <v>130226951</v>
       </c>
       <c r="B4" t="n">
-        <v>98957</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lilla Bråstorp, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537821</v>
+        <v>537736</v>
       </c>
       <c r="R4" t="n">
-        <v>6467932</v>
+        <v>6467965</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,45 +988,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130226328</v>
+        <v>130227576</v>
       </c>
       <c r="B5" t="n">
-        <v>98957</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lilla Bråstorp, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537772</v>
+        <v>537806</v>
       </c>
       <c r="R5" t="n">
-        <v>6467983</v>
+        <v>6467876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130226327</v>
+        <v>130228067</v>
       </c>
       <c r="B6" t="n">
-        <v>96446</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,34 +1104,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lilla Bråstorp, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>537772</v>
+        <v>537809</v>
       </c>
       <c r="R6" t="n">
-        <v>6467983</v>
+        <v>6467952</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,54 +1198,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130226681</v>
+        <v>131553226</v>
       </c>
       <c r="B7" t="n">
-        <v>98957</v>
+        <v>58136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lilla Bråstorp, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>537730</v>
+        <v>537789</v>
       </c>
       <c r="R7" t="n">
-        <v>6468003</v>
+        <v>6467828</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1234,12 +1263,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1259,47 +1288,48 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hasse Andersson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130227576</v>
+        <v>130228374</v>
       </c>
       <c r="B8" t="n">
-        <v>57851</v>
+        <v>8444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1309,10 +1339,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537806</v>
+        <v>537793</v>
       </c>
       <c r="R8" t="n">
-        <v>6467876</v>
+        <v>6467967</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1353,6 +1383,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1364,60 +1395,52 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hasse Andersson</t>
+          <t>Emma Nordenberg, Hasse Andersson, Hasse Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130228067</v>
+        <v>130226109</v>
       </c>
       <c r="B9" t="n">
-        <v>57851</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lilla Bråstorp, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537809</v>
+        <v>537774</v>
       </c>
       <c r="R9" t="n">
-        <v>6467952</v>
+        <v>6467891</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130226435</v>
+        <v>130226255</v>
       </c>
       <c r="B10" t="n">
-        <v>98957</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1504,26 +1527,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lilla Bråstorp, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537773</v>
+        <v>537794</v>
       </c>
       <c r="R10" t="n">
-        <v>6468012</v>
+        <v>6467943</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,10 +1596,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130226109</v>
+        <v>130226321</v>
       </c>
       <c r="B11" t="n">
-        <v>98957</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1610,17 +1624,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lilla Bråstorp, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537774</v>
+        <v>537772</v>
       </c>
       <c r="R11" t="n">
-        <v>6467891</v>
+        <v>6467983</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1679,54 +1702,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130228374</v>
+        <v>130226435</v>
       </c>
       <c r="B12" t="n">
-        <v>8440</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lilla Bråstorp, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537793</v>
+        <v>537773</v>
       </c>
       <c r="R12" t="n">
-        <v>6467967</v>
+        <v>6468012</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1767,7 +1790,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1779,17 +1801,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hasse Andersson, Hasse Andersson</t>
+          <t>Emma Nordenberg, Hasse Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130228095</v>
+        <v>130226578</v>
       </c>
       <c r="B13" t="n">
-        <v>98957</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,7 +1838,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1830,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537824</v>
+        <v>537743</v>
       </c>
       <c r="R13" t="n">
-        <v>6467959</v>
+        <v>6467993</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1892,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130226897</v>
+        <v>130226681</v>
       </c>
       <c r="B14" t="n">
-        <v>98957</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,17 +1942,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lilla Bråstorp, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537736</v>
+        <v>537730</v>
       </c>
       <c r="R14" t="n">
-        <v>6467965</v>
+        <v>6468003</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1989,43 +2020,35 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130226951</v>
+        <v>130226897</v>
       </c>
       <c r="B15" t="n">
-        <v>57851</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lilla Bråstorp, Ög</t>
@@ -2094,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130226578</v>
+        <v>130227792</v>
       </c>
       <c r="B16" t="n">
-        <v>98957</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2122,26 +2145,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lilla Bråstorp, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537743</v>
+        <v>537821</v>
       </c>
       <c r="R16" t="n">
-        <v>6467993</v>
+        <v>6467932</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131470166</v>
+        <v>130228095</v>
       </c>
       <c r="B17" t="n">
-        <v>99054</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2244,10 +2258,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537744</v>
+        <v>537824</v>
       </c>
       <c r="R17" t="n">
-        <v>6467923</v>
+        <v>6467959</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2274,12 +2288,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2299,66 +2313,52 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Emma Nordenberg, Hasse Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131469633</v>
+        <v>130228510</v>
       </c>
       <c r="B18" t="n">
-        <v>91869</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lilla Bråstorp, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537717</v>
+        <v>537793</v>
       </c>
       <c r="R18" t="n">
-        <v>6467941</v>
+        <v>6467967</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2385,12 +2385,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2410,52 +2410,61 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Emma Nordenberg, Hasse Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131553226</v>
+        <v>131470166</v>
       </c>
       <c r="B19" t="n">
-        <v>58073</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lilla Bråstorp, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537789</v>
+        <v>537744</v>
       </c>
       <c r="R19" t="n">
-        <v>6467828</v>
+        <v>6467923</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 55683-2025 artfynd.xlsx
+++ b/artfynd/A 55683-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130226327</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131469633</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130226951</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130227576</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228067</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131553226</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228374</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130226109</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1593,6 +1638,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130226255</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1699,6 +1749,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130226321</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1805,6 +1860,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130226435</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1911,6 +1971,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130226578</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2017,6 +2082,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130226681</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2114,6 +2184,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130226897</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2211,6 +2286,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130227792</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2317,6 +2397,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228095</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2414,6 +2499,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130228510</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2520,8 +2610,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131470166</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>